--- a/data/2026-02-05_BSI-and-TDI_SAS-F-5.xlsx
+++ b/data/2026-02-05_BSI-and-TDI_SAS-F-5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\Documents\A\Utdanning\PhD\05_Analyse-i-R\04_Blood_Speckle_Imaging\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12655915-3462-4F9F-8E91-FF544332F8B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5E550A-C16A-4B56-A03B-C9C094C2C072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
